--- a/originales/respuestas/2025/01. Calificadas/bucle p12/Personería De Bogotá.xlsx
+++ b/originales/respuestas/2025/01. Calificadas/bucle p12/Personería De Bogotá.xlsx
@@ -469,7 +469,13 @@
   </sheetPr>
   <sheetFormatPr customHeight="1" defaultColWidth="14.43" defaultRowHeight="15.0"/>
   <cols>
-    <col customWidth="1" min="1" max="26" width="10.71"/>
+    <col customWidth="1" min="1" max="1" width="10.71"/>
+    <col customWidth="1" min="2" max="2" width="30.86"/>
+    <col customWidth="1" min="3" max="3" width="22.57"/>
+    <col customWidth="1" min="4" max="4" width="27.57"/>
+    <col customWidth="1" min="5" max="5" width="28.86"/>
+    <col customWidth="1" min="6" max="6" width="37.43"/>
+    <col customWidth="1" min="7" max="26" width="10.71"/>
   </cols>
   <sheetData>
     <row r="1" ht="14.25" customHeight="1">
